--- a/DBs/nfl/Results/NFL_2022_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2022_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFFF1D64-CE14-4900-AF2C-7FDEEAD7F679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DB263-6C19-409F-87A6-63498AA56153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1D7F6DC0-A17E-40E2-89C3-58EC05691187}"/>
   </bookViews>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>BUF</t>
-  </si>
-  <si>
-    <t>STL</t>
   </si>
   <si>
     <t>A</t>
@@ -142,12 +139,6 @@
     <t>TEN</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>OAK</t>
-  </si>
-  <si>
     <t>TB</t>
   </si>
   <si>
@@ -176,6 +167,15 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LAC</t>
   </si>
 </sst>
 </file>
@@ -1072,10 +1072,10 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>31</v>
@@ -1101,13 +1101,13 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>10</v>
@@ -1133,13 +1133,13 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4">
         <v>27</v>
@@ -1165,13 +1165,13 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5">
         <v>26</v>
@@ -1197,13 +1197,13 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6">
         <v>26</v>
@@ -1229,13 +1229,13 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7">
         <v>24</v>
@@ -1261,13 +1261,13 @@
         <v>11</v>
       </c>
       <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8">
         <v>19</v>
@@ -1293,13 +1293,13 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -1325,13 +1325,13 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
       <c r="G10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10">
         <v>23</v>
@@ -1357,13 +1357,13 @@
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11">
         <v>20</v>
@@ -1389,13 +1389,13 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" t="s">
         <v>24</v>
       </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12">
         <v>20</v>
@@ -1421,13 +1421,13 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H13">
         <v>20</v>
@@ -1453,13 +1453,13 @@
         <v>11</v>
       </c>
       <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
         <v>26</v>
       </c>
-      <c r="F14" t="s">
-        <v>27</v>
-      </c>
       <c r="G14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H14">
         <v>38</v>
@@ -1485,13 +1485,13 @@
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15">
         <v>35</v>
@@ -1517,13 +1517,13 @@
         <v>11</v>
       </c>
       <c r="E16" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" t="s">
         <v>28</v>
       </c>
-      <c r="F16" t="s">
-        <v>29</v>
-      </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16">
         <v>28</v>
@@ -1549,13 +1549,13 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17">
         <v>22</v>
@@ -1581,13 +1581,13 @@
         <v>11</v>
       </c>
       <c r="E18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" t="s">
         <v>30</v>
       </c>
-      <c r="F18" t="s">
-        <v>31</v>
-      </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18">
         <v>20</v>
@@ -1613,13 +1613,13 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H19">
         <v>7</v>
@@ -1645,13 +1645,13 @@
         <v>11</v>
       </c>
       <c r="E20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" t="s">
         <v>32</v>
       </c>
-      <c r="F20" t="s">
-        <v>33</v>
-      </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20">
         <v>24</v>
@@ -1677,13 +1677,13 @@
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21">
         <v>9</v>
@@ -1709,13 +1709,13 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
       <c r="G22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H22">
         <v>44</v>
@@ -1741,13 +1741,13 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23">
         <v>21</v>
@@ -1773,13 +1773,13 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
         <v>36</v>
       </c>
-      <c r="F24" t="s">
-        <v>37</v>
-      </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24">
         <v>23</v>
@@ -1805,13 +1805,13 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H25">
         <v>7</v>
@@ -1837,13 +1837,13 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" t="s">
         <v>38</v>
       </c>
-      <c r="F26" t="s">
-        <v>39</v>
-      </c>
       <c r="G26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26">
         <v>21</v>
@@ -1869,13 +1869,13 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27">
         <v>20</v>
@@ -1901,13 +1901,13 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28">
         <v>24</v>
@@ -1933,13 +1933,13 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H29">
         <v>19</v>
@@ -1965,13 +1965,13 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H30">
         <v>19</v>
@@ -1997,13 +1997,13 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31">
         <v>3</v>
@@ -2029,13 +2029,13 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32">
         <v>17</v>
@@ -2061,13 +2061,13 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H33">
         <v>16</v>
@@ -2093,13 +2093,13 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34">
         <v>27</v>
@@ -2125,13 +2125,13 @@
         <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H35">
         <v>24</v>
@@ -2157,13 +2157,13 @@
         <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36">
         <v>19</v>
@@ -2189,13 +2189,13 @@
         <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H37">
         <v>16</v>
@@ -2221,13 +2221,13 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H38">
         <v>31</v>
@@ -2253,13 +2253,13 @@
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39">
         <v>30</v>
@@ -2285,13 +2285,13 @@
         <v>11</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40">
         <v>24</v>
@@ -2317,13 +2317,13 @@
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2349,13 +2349,13 @@
         <v>11</v>
       </c>
       <c r="E42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F42" t="s">
         <v>27</v>
       </c>
-      <c r="F42" t="s">
-        <v>28</v>
-      </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42">
         <v>36</v>
@@ -2381,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H43">
         <v>27</v>
@@ -2413,13 +2413,13 @@
         <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H44">
         <v>42</v>
@@ -2445,13 +2445,13 @@
         <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H45">
         <v>38</v>
@@ -2477,13 +2477,13 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H46">
         <v>20</v>
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47">
         <v>10</v>
@@ -2541,13 +2541,13 @@
         <v>11</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H48">
         <v>17</v>
@@ -2573,13 +2573,13 @@
         <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49">
         <v>14</v>
@@ -2605,13 +2605,13 @@
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50">
         <v>31</v>
@@ -2637,13 +2637,13 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H51">
         <v>27</v>
@@ -2669,13 +2669,13 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52">
         <v>27</v>
@@ -2701,13 +2701,13 @@
         <v>11</v>
       </c>
       <c r="E53" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53">
         <v>7</v>
@@ -2733,13 +2733,13 @@
         <v>11</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54">
         <v>20</v>
@@ -2765,13 +2765,13 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H55">
         <v>17</v>
@@ -2797,13 +2797,13 @@
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F56" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H56">
         <v>29</v>
@@ -2829,13 +2829,13 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57">
         <v>23</v>
@@ -2861,13 +2861,13 @@
         <v>11</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58">
         <v>16</v>
@@ -2893,13 +2893,13 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H59">
         <v>9</v>
@@ -2925,13 +2925,13 @@
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60">
         <v>27</v>
@@ -2957,13 +2957,13 @@
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H61">
         <v>10</v>
@@ -2992,10 +2992,10 @@
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62">
         <v>41</v>
@@ -3021,13 +3021,13 @@
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F63" t="s">
         <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H63">
         <v>7</v>
@@ -3053,13 +3053,13 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64">
         <v>24</v>
@@ -3085,13 +3085,13 @@
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H65">
         <v>7</v>
@@ -3117,13 +3117,13 @@
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H66">
         <v>29</v>
@@ -3149,13 +3149,13 @@
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H67">
         <v>17</v>
@@ -3181,13 +3181,13 @@
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F68" t="s">
         <v>12</v>
       </c>
       <c r="G68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H68">
         <v>21</v>
@@ -3216,10 +3216,10 @@
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H69">
         <v>19</v>
@@ -3245,13 +3245,13 @@
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H70">
         <v>22</v>
@@ -3277,13 +3277,13 @@
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H71">
         <v>14</v>
@@ -3309,13 +3309,13 @@
         <v>11</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H72">
         <v>23</v>
@@ -3341,13 +3341,13 @@
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H73">
         <v>20</v>
@@ -3373,13 +3373,13 @@
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H74">
         <v>27</v>
@@ -3405,13 +3405,13 @@
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H75">
         <v>12</v>
@@ -3437,13 +3437,13 @@
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H76">
         <v>20</v>
@@ -3469,13 +3469,13 @@
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H77">
         <v>17</v>
@@ -3501,13 +3501,13 @@
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H78">
         <v>28</v>
@@ -3533,13 +3533,13 @@
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H79">
         <v>24</v>
@@ -3565,13 +3565,13 @@
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H80">
         <v>37</v>
@@ -3597,13 +3597,13 @@
         <v>11</v>
       </c>
       <c r="E81" t="s">
+        <v>30</v>
+      </c>
+      <c r="F81" t="s">
         <v>31</v>
       </c>
-      <c r="F81" t="s">
-        <v>32</v>
-      </c>
       <c r="G81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H81">
         <v>26</v>
@@ -3629,13 +3629,13 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F82" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H82">
         <v>24</v>
@@ -3661,13 +3661,13 @@
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F83" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H83">
         <v>22</v>
@@ -3693,13 +3693,13 @@
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H84">
         <v>24</v>
@@ -3725,13 +3725,13 @@
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -3757,13 +3757,13 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H86">
         <v>38</v>
@@ -3789,13 +3789,13 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H87">
         <v>10</v>
@@ -3821,13 +3821,13 @@
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F88" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H88">
         <v>27</v>
@@ -3853,13 +3853,13 @@
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G89" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H89">
         <v>23</v>
@@ -3885,13 +3885,13 @@
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F90" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H90">
         <v>20</v>
@@ -3917,13 +3917,13 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H91">
         <v>12</v>
@@ -3949,13 +3949,13 @@
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H92">
         <v>14</v>
@@ -3981,13 +3981,13 @@
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H93">
         <v>12</v>
@@ -4013,13 +4013,13 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G94" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H94">
         <v>11</v>
@@ -4045,13 +4045,13 @@
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H95">
         <v>10</v>
@@ -4077,13 +4077,13 @@
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G96" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H96">
         <v>23</v>
@@ -4109,13 +4109,13 @@
         <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F97" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H97">
         <v>16</v>
@@ -4141,13 +4141,13 @@
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H98">
         <v>27</v>
@@ -4173,13 +4173,13 @@
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H99">
         <v>15</v>
@@ -4205,13 +4205,13 @@
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H100">
         <v>28</v>
@@ -4237,13 +4237,13 @@
         <v>11</v>
       </c>
       <c r="E101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H101">
         <v>25</v>
@@ -4269,13 +4269,13 @@
         <v>11</v>
       </c>
       <c r="E102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F102" t="s">
         <v>17</v>
       </c>
-      <c r="F102" t="s">
-        <v>18</v>
-      </c>
       <c r="G102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H102">
         <v>23</v>
@@ -4301,13 +4301,13 @@
         <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H103">
         <v>20</v>
@@ -4336,10 +4336,10 @@
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H104">
         <v>23</v>
@@ -4365,13 +4365,13 @@
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F105" t="s">
         <v>12</v>
       </c>
       <c r="G105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H105">
         <v>20</v>
@@ -4397,13 +4397,13 @@
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H106">
         <v>20</v>
@@ -4429,13 +4429,13 @@
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G107" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H107">
         <v>12</v>
@@ -4461,13 +4461,13 @@
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G108" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H108">
         <v>24</v>
@@ -4493,13 +4493,13 @@
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F109" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G109" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H109">
         <v>17</v>
@@ -4525,13 +4525,13 @@
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F110" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H110">
         <v>25</v>
@@ -4557,13 +4557,13 @@
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G111" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H111">
         <v>10</v>
@@ -4589,13 +4589,13 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F112" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G112" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H112">
         <v>48</v>
@@ -4621,13 +4621,13 @@
         <v>11</v>
       </c>
       <c r="E113" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F113" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H113">
         <v>45</v>
@@ -4653,13 +4653,13 @@
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G114" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H114">
         <v>34</v>
@@ -4685,13 +4685,13 @@
         <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F115" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H115">
         <v>24</v>
@@ -4717,13 +4717,13 @@
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F116" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H116">
         <v>29</v>
@@ -4749,13 +4749,13 @@
         <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F117" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G117" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H117">
         <v>21</v>
@@ -4781,13 +4781,13 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F118" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G118" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H118">
         <v>24</v>
@@ -4813,13 +4813,13 @@
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F119" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G119" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H119">
         <v>20</v>
@@ -4845,13 +4845,13 @@
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G120" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H120">
         <v>26</v>
@@ -4877,13 +4877,13 @@
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F121" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G121" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H121">
         <v>16</v>
@@ -4909,13 +4909,13 @@
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F122" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H122">
         <v>32</v>
@@ -4941,13 +4941,13 @@
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F123" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G123" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H123">
         <v>23</v>
@@ -4973,13 +4973,13 @@
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G124" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H124">
         <v>27</v>
@@ -5005,13 +5005,13 @@
         <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F125" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G125" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H125">
         <v>24</v>
@@ -5037,13 +5037,13 @@
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F126" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G126" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H126">
         <v>41</v>
@@ -5069,13 +5069,13 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F127" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H127">
         <v>31</v>
@@ -5101,13 +5101,13 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F128" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G128" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H128">
         <v>24</v>
@@ -5133,13 +5133,13 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F129" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H129">
         <v>9</v>
@@ -5165,13 +5165,13 @@
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F130" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G130" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H130">
         <v>12</v>
@@ -5197,13 +5197,13 @@
         <v>11</v>
       </c>
       <c r="E131" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H131">
         <v>9</v>
@@ -5229,13 +5229,13 @@
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F132" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H132">
         <v>27</v>
@@ -5261,13 +5261,13 @@
         <v>11</v>
       </c>
       <c r="E133" t="s">
+        <v>36</v>
+      </c>
+      <c r="F133" t="s">
         <v>37</v>
       </c>
-      <c r="F133" t="s">
-        <v>38</v>
-      </c>
       <c r="G133" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H133">
         <v>22</v>
@@ -5293,13 +5293,13 @@
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F134" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H134">
         <v>21</v>
@@ -5325,13 +5325,13 @@
         <v>11</v>
       </c>
       <c r="E135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G135" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H135">
         <v>15</v>
@@ -5360,10 +5360,10 @@
         <v>12</v>
       </c>
       <c r="F136" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H136">
         <v>38</v>
@@ -5389,13 +5389,13 @@
         <v>11</v>
       </c>
       <c r="E137" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F137" t="s">
         <v>12</v>
       </c>
       <c r="G137" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H137">
         <v>3</v>
@@ -5421,13 +5421,13 @@
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G138" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H138">
         <v>29</v>
@@ -5453,13 +5453,13 @@
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F139" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G139" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H139">
         <v>22</v>
@@ -5485,13 +5485,13 @@
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F140" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G140" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H140">
         <v>30</v>
@@ -5517,13 +5517,13 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F141" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G141" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H141">
         <v>28</v>
@@ -5549,13 +5549,13 @@
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F142" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G142" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H142">
         <v>29</v>
@@ -5581,13 +5581,13 @@
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H143">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F144" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G144" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H144">
         <v>13</v>
@@ -5645,13 +5645,13 @@
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F145" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G145" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H145">
         <v>6</v>
@@ -5677,13 +5677,13 @@
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F146" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G146" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H146">
         <v>40</v>
@@ -5709,13 +5709,13 @@
         <v>11</v>
       </c>
       <c r="E147" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F147" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G147" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H147">
         <v>17</v>
@@ -5741,13 +5741,13 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F148" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H148">
         <v>39</v>
@@ -5773,13 +5773,13 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F149" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G149" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H149">
         <v>32</v>
@@ -5805,13 +5805,13 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F150" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G150" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H150">
         <v>21</v>
@@ -5837,13 +5837,13 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F151" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H151">
         <v>17</v>
@@ -5869,13 +5869,13 @@
         <v>11</v>
       </c>
       <c r="E152" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F152" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G152" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H152">
         <v>37</v>
@@ -5901,13 +5901,13 @@
         <v>11</v>
       </c>
       <c r="E153" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F153" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H153">
         <v>15</v>
@@ -5933,13 +5933,13 @@
         <v>11</v>
       </c>
       <c r="E154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F154" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G154" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H154">
         <v>20</v>
@@ -5965,13 +5965,13 @@
         <v>11</v>
       </c>
       <c r="E155" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F155" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G155" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H155">
         <v>17</v>
@@ -5997,13 +5997,13 @@
         <v>11</v>
       </c>
       <c r="E156" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F156" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G156" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H156">
         <v>22</v>
@@ -6029,13 +6029,13 @@
         <v>11</v>
       </c>
       <c r="E157" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F157" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G157" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H157">
         <v>10</v>
@@ -6061,13 +6061,13 @@
         <v>11</v>
       </c>
       <c r="E158" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F158" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H158">
         <v>19</v>
@@ -6093,13 +6093,13 @@
         <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F159" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G159" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H159">
         <v>17</v>
@@ -6125,13 +6125,13 @@
         <v>11</v>
       </c>
       <c r="E160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F160" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G160" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H160">
         <v>30</v>
@@ -6157,13 +6157,13 @@
         <v>11</v>
       </c>
       <c r="E161" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F161" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G161" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H161">
         <v>29</v>
@@ -6189,13 +6189,13 @@
         <v>11</v>
       </c>
       <c r="E162" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G162" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H162">
         <v>12</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="E163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F163" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H163">
         <v>7</v>
@@ -6253,13 +6253,13 @@
         <v>11</v>
       </c>
       <c r="E164" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G164" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H164">
         <v>28</v>
@@ -6285,13 +6285,13 @@
         <v>11</v>
       </c>
       <c r="E165" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F165" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G165" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H165">
         <v>14</v>
@@ -6317,13 +6317,13 @@
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G166" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H166">
         <v>30</v>
@@ -6349,13 +6349,13 @@
         <v>11</v>
       </c>
       <c r="E167" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F167" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G167" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H167">
         <v>26</v>
@@ -6381,13 +6381,13 @@
         <v>11</v>
       </c>
       <c r="E168" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G168" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H168">
         <v>38</v>
@@ -6413,13 +6413,13 @@
         <v>11</v>
       </c>
       <c r="E169" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G169" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H169">
         <v>15</v>
@@ -6445,13 +6445,13 @@
         <v>11</v>
       </c>
       <c r="E170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F170" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G170" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H170">
         <v>34</v>
@@ -6477,13 +6477,13 @@
         <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F171" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G171" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H171">
         <v>27</v>
@@ -6509,13 +6509,13 @@
         <v>11</v>
       </c>
       <c r="E172" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F172" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G172" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H172">
         <v>27</v>
@@ -6541,13 +6541,13 @@
         <v>11</v>
       </c>
       <c r="E173" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F173" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H173">
         <v>10</v>
@@ -6573,13 +6573,13 @@
         <v>11</v>
       </c>
       <c r="E174" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F174" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G174" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H174">
         <v>24</v>
@@ -6605,13 +6605,13 @@
         <v>11</v>
       </c>
       <c r="E175" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F175" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G175" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H175">
         <v>16</v>
@@ -6637,13 +6637,13 @@
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F176" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G176" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H176">
         <v>24</v>
@@ -6669,13 +6669,13 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F177" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G177" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H177">
         <v>20</v>
@@ -6701,13 +6701,13 @@
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F178" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G178" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H178">
         <v>20</v>
@@ -6733,13 +6733,13 @@
         <v>11</v>
       </c>
       <c r="E179" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F179" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G179" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H179">
         <v>18</v>
@@ -6765,13 +6765,13 @@
         <v>11</v>
       </c>
       <c r="E180" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F180" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G180" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H180">
         <v>24</v>
@@ -6797,13 +6797,13 @@
         <v>11</v>
       </c>
       <c r="E181" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F181" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G181" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H181">
         <v>10</v>
@@ -6829,13 +6829,13 @@
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F182" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G182" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H182">
         <v>19</v>
@@ -6861,13 +6861,13 @@
         <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F183" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G183" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H183">
         <v>9</v>
@@ -6896,10 +6896,10 @@
         <v>12</v>
       </c>
       <c r="F184" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G184" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H184">
         <v>24</v>
@@ -6925,13 +6925,13 @@
         <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F185" t="s">
         <v>12</v>
       </c>
       <c r="G185" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H185">
         <v>20</v>
@@ -6957,13 +6957,13 @@
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F186" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H186">
         <v>26</v>
@@ -6989,13 +6989,13 @@
         <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F187" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G187" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H187">
         <v>17</v>
@@ -7021,13 +7021,13 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F188" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G188" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H188">
         <v>19</v>
@@ -7053,13 +7053,13 @@
         <v>11</v>
       </c>
       <c r="E189" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F189" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G189" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H189">
         <v>16</v>
@@ -7085,13 +7085,13 @@
         <v>11</v>
       </c>
       <c r="E190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F190" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G190" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H190">
         <v>42</v>
@@ -7117,13 +7117,13 @@
         <v>11</v>
       </c>
       <c r="E191" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F191" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G191" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H191">
         <v>34</v>
@@ -7149,13 +7149,13 @@
         <v>11</v>
       </c>
       <c r="E192" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H192">
         <v>35</v>
@@ -7181,13 +7181,13 @@
         <v>11</v>
       </c>
       <c r="E193" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F193" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G193" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H193">
         <v>17</v>
@@ -7213,13 +7213,13 @@
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F194" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G194" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H194">
         <v>21</v>
@@ -7245,13 +7245,13 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F195" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G195" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H195">
         <v>3</v>
@@ -7277,13 +7277,13 @@
         <v>11</v>
       </c>
       <c r="E196" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G196" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H196">
         <v>23</v>
@@ -7309,13 +7309,13 @@
         <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F197" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G197" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H197">
         <v>20</v>
@@ -7341,13 +7341,13 @@
         <v>11</v>
       </c>
       <c r="E198" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F198" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G198" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H198">
         <v>19</v>
@@ -7373,13 +7373,13 @@
         <v>11</v>
       </c>
       <c r="E199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F199" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G199" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H199">
         <v>10</v>
@@ -7405,13 +7405,13 @@
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F200" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G200" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H200">
         <v>24</v>
@@ -7437,13 +7437,13 @@
         <v>11</v>
       </c>
       <c r="E201" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F201" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G201" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H201">
         <v>6</v>
@@ -7469,13 +7469,13 @@
         <v>11</v>
       </c>
       <c r="E202" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F202" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G202" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H202">
         <v>23</v>
@@ -7501,13 +7501,13 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F203" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G203" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H203">
         <v>21</v>
@@ -7533,13 +7533,13 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F204" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G204" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H204">
         <v>23</v>
@@ -7565,13 +7565,13 @@
         <v>11</v>
       </c>
       <c r="E205" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F205" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G205" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H205">
         <v>17</v>
@@ -7597,13 +7597,13 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F206" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G206" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H206">
         <v>38</v>
@@ -7629,13 +7629,13 @@
         <v>11</v>
       </c>
       <c r="E207" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F207" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G207" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H207">
         <v>20</v>
@@ -7661,13 +7661,13 @@
         <v>11</v>
       </c>
       <c r="E208" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F208" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G208" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H208">
         <v>16</v>
@@ -7693,13 +7693,13 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F209" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G209" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H209">
         <v>9</v>
@@ -7725,13 +7725,13 @@
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F210" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G210" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H210">
         <v>44</v>
@@ -7757,13 +7757,13 @@
         <v>11</v>
       </c>
       <c r="E211" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F211" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G211" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H211">
         <v>23</v>
@@ -7789,13 +7789,13 @@
         <v>11</v>
       </c>
       <c r="E212" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F212" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G212" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H212">
         <v>37</v>
@@ -7821,13 +7821,13 @@
         <v>11</v>
       </c>
       <c r="E213" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F213" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G213" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H213">
         <v>23</v>
@@ -7853,13 +7853,13 @@
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F214" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G214" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H214">
         <v>16</v>
@@ -7885,13 +7885,13 @@
         <v>11</v>
       </c>
       <c r="E215" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F215" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G215" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H215">
         <v>10</v>
@@ -7917,13 +7917,13 @@
         <v>11</v>
       </c>
       <c r="E216" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F216" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G216" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H216">
         <v>33</v>
@@ -7949,13 +7949,13 @@
         <v>11</v>
       </c>
       <c r="E217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F217" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G217" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H217">
         <v>14</v>
@@ -7981,13 +7981,13 @@
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F218" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G218" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H218">
         <v>27</v>
@@ -8013,13 +8013,13 @@
         <v>11</v>
       </c>
       <c r="E219" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F219" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G219" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H219">
         <v>22</v>
@@ -8045,13 +8045,13 @@
         <v>11</v>
       </c>
       <c r="E220" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F220" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G220" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H220">
         <v>21</v>
@@ -8077,13 +8077,13 @@
         <v>11</v>
       </c>
       <c r="E221" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F221" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G221" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H221">
         <v>17</v>
@@ -8109,13 +8109,13 @@
         <v>11</v>
       </c>
       <c r="E222" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F222" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G222" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H222">
         <v>31</v>
@@ -8141,13 +8141,13 @@
         <v>11</v>
       </c>
       <c r="E223" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F223" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G223" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H223">
         <v>27</v>
@@ -8173,13 +8173,13 @@
         <v>11</v>
       </c>
       <c r="E224" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F224" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G224" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H224">
         <v>35</v>
@@ -8205,13 +8205,13 @@
         <v>11</v>
       </c>
       <c r="E225" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F225" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G225" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H225">
         <v>13</v>
@@ -8237,13 +8237,13 @@
         <v>11</v>
       </c>
       <c r="E226" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F226" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G226" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H226">
         <v>37</v>
@@ -8269,13 +8269,13 @@
         <v>11</v>
       </c>
       <c r="E227" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G227" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H227">
         <v>34</v>
@@ -8301,13 +8301,13 @@
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F228" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G228" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H228">
         <v>49</v>
@@ -8333,13 +8333,13 @@
         <v>11</v>
       </c>
       <c r="E229" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F229" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G229" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H229">
         <v>29</v>
@@ -8365,13 +8365,13 @@
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F230" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G230" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H230">
         <v>34</v>
@@ -8397,13 +8397,13 @@
         <v>11</v>
       </c>
       <c r="E231" t="s">
+        <v>34</v>
+      </c>
+      <c r="F231" t="s">
         <v>35</v>
       </c>
-      <c r="F231" t="s">
-        <v>36</v>
-      </c>
       <c r="G231" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H231">
         <v>26</v>
@@ -8429,13 +8429,13 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F232" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G232" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H232">
         <v>24</v>
@@ -8461,13 +8461,13 @@
         <v>11</v>
       </c>
       <c r="E233" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F233" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G233" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H233">
         <v>0</v>
@@ -8493,13 +8493,13 @@
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F234" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G234" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H234">
         <v>22</v>
@@ -8525,13 +8525,13 @@
         <v>11</v>
       </c>
       <c r="E235" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F235" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H235">
         <v>17</v>
@@ -8557,13 +8557,13 @@
         <v>11</v>
       </c>
       <c r="E236" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F236" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G236" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H236">
         <v>17</v>
@@ -8589,13 +8589,13 @@
         <v>11</v>
       </c>
       <c r="E237" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F237" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G237" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H237">
         <v>10</v>
@@ -8621,13 +8621,13 @@
         <v>11</v>
       </c>
       <c r="E238" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F238" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G238" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H238">
         <v>31</v>
@@ -8653,13 +8653,13 @@
         <v>11</v>
       </c>
       <c r="E239" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F239" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G239" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H239">
         <v>14</v>
@@ -8685,13 +8685,13 @@
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F240" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G240" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H240">
         <v>17</v>
@@ -8717,13 +8717,13 @@
         <v>11</v>
       </c>
       <c r="E241" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F241" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G241" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H241">
         <v>16</v>
@@ -8749,13 +8749,13 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F242" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G242" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H242">
         <v>27</v>
@@ -8781,13 +8781,13 @@
         <v>11</v>
       </c>
       <c r="E243" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F243" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G243" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H243">
         <v>13</v>
@@ -8816,10 +8816,10 @@
         <v>12</v>
       </c>
       <c r="F244" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G244" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H244">
         <v>27</v>
@@ -8845,13 +8845,13 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F245" t="s">
         <v>12</v>
       </c>
       <c r="G245" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H245">
         <v>17</v>
@@ -8877,13 +8877,13 @@
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F246" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G246" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H246">
         <v>32</v>
@@ -8909,13 +8909,13 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G247" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H247">
         <v>13</v>
@@ -8941,13 +8941,13 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G248" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H248">
         <v>29</v>
@@ -8973,13 +8973,13 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F249" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G249" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H249">
         <v>17</v>
@@ -9005,13 +9005,13 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F250" t="s">
         <v>12</v>
       </c>
       <c r="G250" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H250">
         <v>20</v>
@@ -9040,10 +9040,10 @@
         <v>12</v>
       </c>
       <c r="F251" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G251" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H251">
         <v>17</v>
@@ -9069,13 +9069,13 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F252" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G252" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H252">
         <v>15</v>
@@ -9101,13 +9101,13 @@
         <v>11</v>
       </c>
       <c r="E253" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F253" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G253" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H253">
         <v>9</v>
@@ -9133,13 +9133,13 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F254" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G254" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H254">
         <v>20</v>
@@ -9165,13 +9165,13 @@
         <v>11</v>
       </c>
       <c r="E255" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F255" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G255" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H255">
         <v>17</v>
@@ -9197,13 +9197,13 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F256" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G256" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H256">
         <v>20</v>
@@ -9229,13 +9229,13 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F257" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G257" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H257">
         <v>17</v>
@@ -9261,13 +9261,13 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F258" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G258" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H258">
         <v>42</v>
@@ -9293,13 +9293,13 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F259" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G259" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H259">
         <v>21</v>
@@ -9325,13 +9325,13 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F260" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G260" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H260">
         <v>35</v>
@@ -9357,13 +9357,13 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F261" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G261" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H261">
         <v>32</v>
@@ -9389,13 +9389,13 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F262" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G262" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H262">
         <v>26</v>
@@ -9421,13 +9421,13 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F263" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G263" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H263">
         <v>3</v>
@@ -9453,13 +9453,13 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F264" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G264" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H264">
         <v>27</v>
@@ -9485,13 +9485,13 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F265" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G265" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H265">
         <v>20</v>
@@ -9517,13 +9517,13 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F266" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G266" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H266">
         <v>31</v>
@@ -9549,13 +9549,13 @@
         <v>11</v>
       </c>
       <c r="E267" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F267" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G267" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H267">
         <v>21</v>
@@ -9581,13 +9581,13 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F268" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G268" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H268">
         <v>16</v>
@@ -9613,13 +9613,13 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F269" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G269" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H269">
         <v>13</v>
@@ -9645,13 +9645,13 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F270" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G270" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H270">
         <v>20</v>
@@ -9677,13 +9677,13 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F271" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G271" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H271">
         <v>17</v>
@@ -9709,13 +9709,13 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F272" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G272" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H272">
         <v>27</v>
@@ -9741,13 +9741,13 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F273" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G273" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H273">
         <v>13</v>
@@ -9773,13 +9773,13 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F274" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G274" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H274">
         <v>25</v>
@@ -9805,13 +9805,13 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F275" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G275" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H275">
         <v>15</v>
@@ -9837,13 +9837,13 @@
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F276" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G276" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H276">
         <v>21</v>
@@ -9869,13 +9869,13 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F277" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G277" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H277">
         <v>16</v>
@@ -9901,13 +9901,13 @@
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F278" t="s">
         <v>12</v>
       </c>
       <c r="G278" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H278">
         <v>33</v>
@@ -9936,10 +9936,10 @@
         <v>12</v>
       </c>
       <c r="F279" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G279" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H279">
         <v>30</v>
@@ -9965,13 +9965,13 @@
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F280" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G280" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H280">
         <v>39</v>
@@ -9997,13 +9997,13 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F281" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G281" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H281">
         <v>17</v>
@@ -10029,13 +10029,13 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F282" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G282" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H282">
         <v>17</v>
@@ -10061,13 +10061,13 @@
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F283" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G283" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H283">
         <v>10</v>
@@ -10093,13 +10093,13 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F284" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G284" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H284">
         <v>24</v>
@@ -10125,13 +10125,13 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F285" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G285" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H285">
         <v>16</v>
@@ -10157,13 +10157,13 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F286" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G286" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H286">
         <v>31</v>
@@ -10189,13 +10189,13 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F287" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G287" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H287">
         <v>30</v>
@@ -10221,13 +10221,13 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F288" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G288" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H288">
         <v>27</v>
@@ -10253,13 +10253,13 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F289" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G289" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H289">
         <v>17</v>
@@ -10285,13 +10285,13 @@
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F290" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G290" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H290">
         <v>20</v>
@@ -10317,13 +10317,13 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F291" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G291" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H291">
         <v>10</v>
@@ -10349,13 +10349,13 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F292" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G292" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H292">
         <v>25</v>
@@ -10381,13 +10381,13 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F293" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H293">
         <v>20</v>
@@ -10413,13 +10413,13 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F294" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G294" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H294">
         <v>31</v>
@@ -10445,13 +10445,13 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F295" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G295" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H295">
         <v>28</v>
@@ -10477,13 +10477,13 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F296" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G296" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H296">
         <v>27</v>
@@ -10509,13 +10509,13 @@
         <v>11</v>
       </c>
       <c r="E297" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F297" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G297" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H297">
         <v>17</v>
@@ -10541,13 +10541,13 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F298" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G298" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H298">
         <v>22</v>
@@ -10573,13 +10573,13 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F299" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G299" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H299">
         <v>16</v>
@@ -10605,13 +10605,13 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F300" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G300" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H300">
         <v>32</v>
@@ -10637,13 +10637,13 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F301" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G301" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H301">
         <v>21</v>
@@ -10669,13 +10669,13 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F302" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G302" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H302">
         <v>27</v>
@@ -10701,13 +10701,13 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F303" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G303" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H303">
         <v>17</v>
@@ -10736,10 +10736,10 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G304" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H304">
         <v>31</v>
@@ -10765,13 +10765,13 @@
         <v>11</v>
       </c>
       <c r="E305" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F305" t="s">
         <v>12</v>
       </c>
       <c r="G305" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H305">
         <v>23</v>
@@ -10797,13 +10797,13 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F306" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G306" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H306">
         <v>31</v>
@@ -10829,13 +10829,13 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F307" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G307" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H307">
         <v>18</v>
@@ -10861,13 +10861,13 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F308" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G308" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H308">
         <v>23</v>
@@ -10893,13 +10893,13 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F309" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G309" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H309">
         <v>10</v>
@@ -10925,13 +10925,13 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F310" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G310" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H310">
         <v>10</v>
@@ -10957,13 +10957,13 @@
         <v>11</v>
       </c>
       <c r="E311" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F311" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G311" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H311">
         <v>3</v>
@@ -10989,13 +10989,13 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F312" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G312" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H312">
         <v>27</v>
@@ -11021,13 +11021,13 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F313" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G313" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H313">
         <v>24</v>
@@ -11053,13 +11053,13 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F314" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G314" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H314">
         <v>13</v>
@@ -11085,13 +11085,13 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F315" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G315" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H315">
         <v>3</v>
@@ -11117,13 +11117,13 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F316" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G316" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H316">
         <v>17</v>
@@ -11149,13 +11149,13 @@
         <v>11</v>
       </c>
       <c r="E317" t="s">
+        <v>24</v>
+      </c>
+      <c r="F317" t="s">
         <v>25</v>
       </c>
-      <c r="F317" t="s">
-        <v>26</v>
-      </c>
       <c r="G317" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H317">
         <v>16</v>
@@ -11181,13 +11181,13 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F318" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G318" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H318">
         <v>27</v>
@@ -11213,13 +11213,13 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F319" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G319" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H319">
         <v>20</v>
@@ -11245,13 +11245,13 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F320" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G320" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H320">
         <v>22</v>
@@ -11277,13 +11277,13 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F321" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G321" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H321">
         <v>16</v>
@@ -11309,13 +11309,13 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F322" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G322" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H322">
         <v>37</v>
@@ -11341,13 +11341,13 @@
         <v>11</v>
       </c>
       <c r="E323" t="s">
+        <v>21</v>
+      </c>
+      <c r="F323" t="s">
         <v>22</v>
       </c>
-      <c r="F323" t="s">
-        <v>23</v>
-      </c>
       <c r="G323" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H323">
         <v>30</v>
@@ -11373,13 +11373,13 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F324" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G324" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H324">
         <v>40</v>
@@ -11405,13 +11405,13 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F325" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G325" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H325">
         <v>3</v>
@@ -11437,13 +11437,13 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F326" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G326" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H326">
         <v>30</v>
@@ -11469,13 +11469,13 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F327" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G327" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H327">
         <v>27</v>
@@ -11501,13 +11501,13 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F328" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G328" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H328">
         <v>38</v>
@@ -11533,13 +11533,13 @@
         <v>11</v>
       </c>
       <c r="E329" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F329" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G329" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H329">
         <v>10</v>
@@ -11568,10 +11568,10 @@
         <v>12</v>
       </c>
       <c r="F330" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G330" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H330">
         <v>28</v>
@@ -11597,13 +11597,13 @@
         <v>11</v>
       </c>
       <c r="E331" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F331" t="s">
         <v>12</v>
       </c>
       <c r="G331" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H331">
         <v>25</v>
@@ -11629,13 +11629,13 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F332" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G332" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H332">
         <v>28</v>
@@ -11661,13 +11661,13 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F333" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G333" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H333">
         <v>20</v>
@@ -11693,13 +11693,13 @@
         <v>11</v>
       </c>
       <c r="E334" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F334" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G334" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H334">
         <v>33</v>
@@ -11725,13 +11725,13 @@
         <v>11</v>
       </c>
       <c r="E335" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F335" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G335" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H335">
         <v>26</v>
@@ -11757,13 +11757,13 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F336" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G336" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H336">
         <v>20</v>
@@ -11789,13 +11789,13 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F337" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G337" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H337">
         <v>16</v>
@@ -11821,13 +11821,13 @@
         <v>11</v>
       </c>
       <c r="E338" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F338" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G338" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H338">
         <v>23</v>
@@ -11853,13 +11853,13 @@
         <v>11</v>
       </c>
       <c r="E339" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F339" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G339" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H339">
         <v>17</v>
@@ -11885,13 +11885,13 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F340" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G340" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H340">
         <v>30</v>
@@ -11917,13 +11917,13 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F341" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G341" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H341">
         <v>15</v>
@@ -11949,13 +11949,13 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F342" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G342" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H342">
         <v>28</v>
@@ -11981,13 +11981,13 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F343" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G343" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H343">
         <v>27</v>
@@ -12013,13 +12013,13 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F344" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G344" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H344">
         <v>19</v>
@@ -12045,13 +12045,13 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F345" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G345" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H345">
         <v>13</v>
@@ -12077,13 +12077,13 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F346" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G346" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H346">
         <v>23</v>
@@ -12109,13 +12109,13 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F347" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G347" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H347">
         <v>10</v>
@@ -12141,13 +12141,13 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F348" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G348" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H348">
         <v>31</v>
@@ -12173,13 +12173,13 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F349" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G349" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H349">
         <v>10</v>
@@ -12205,13 +12205,13 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
+        <v>49</v>
+      </c>
+      <c r="F350" t="s">
         <v>41</v>
       </c>
-      <c r="F350" t="s">
-        <v>44</v>
-      </c>
       <c r="G350" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H350">
         <v>40</v>
@@ -12237,13 +12237,13 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F351" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G351" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H351">
         <v>34</v>
@@ -12269,13 +12269,13 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F352" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G352" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H352">
         <v>25</v>
@@ -12301,13 +12301,13 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F353" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G353" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H353">
         <v>24</v>
@@ -12333,13 +12333,13 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F354" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G354" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H354">
         <v>26</v>
@@ -12365,13 +12365,13 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F355" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G355" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H355">
         <v>10</v>
@@ -12397,13 +12397,13 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F356" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G356" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H356">
         <v>13</v>
@@ -12429,13 +12429,13 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F357" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G357" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H357">
         <v>0</v>
@@ -12461,13 +12461,13 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F358" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G358" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H358">
         <v>40</v>
@@ -12493,13 +12493,13 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F359" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G359" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H359">
         <v>33</v>
@@ -12525,13 +12525,13 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F360" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G360" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H360">
         <v>24</v>
@@ -12557,13 +12557,13 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F361" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G361" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H361">
         <v>17</v>
@@ -12592,10 +12592,10 @@
         <v>12</v>
       </c>
       <c r="F362" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G362" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H362">
         <v>24</v>
@@ -12621,13 +12621,13 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F363" t="s">
         <v>12</v>
       </c>
       <c r="G363" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H363">
         <v>10</v>
@@ -12653,13 +12653,13 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F364" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G364" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H364">
         <v>27</v>
@@ -12685,13 +12685,13 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F365" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G365" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H365">
         <v>14</v>
@@ -12717,13 +12717,13 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F366" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G366" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H366">
         <v>10</v>
@@ -12749,13 +12749,13 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F367" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G367" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H367">
         <v>9</v>
@@ -12781,13 +12781,13 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F368" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G368" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H368">
         <v>40</v>
@@ -12813,13 +12813,13 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F369" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G369" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H369">
         <v>14</v>
@@ -12845,13 +12845,13 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F370" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G370" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H370">
         <v>27</v>
@@ -12877,13 +12877,13 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F371" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G371" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H371">
         <v>22</v>
@@ -12909,13 +12909,13 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F372" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G372" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H372">
         <v>20</v>
@@ -12941,13 +12941,13 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F373" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G373" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H373">
         <v>20</v>
@@ -12973,13 +12973,13 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F374" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G374" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H374">
         <v>35</v>
@@ -13005,13 +13005,13 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F375" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G375" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H375">
         <v>10</v>
@@ -13037,13 +13037,13 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F376" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G376" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H376">
         <v>19</v>
@@ -13069,13 +13069,13 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F377" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G377" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H377">
         <v>16</v>
@@ -13101,13 +13101,13 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F378" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G378" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H378">
         <v>28</v>
@@ -13133,13 +13133,13 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F379" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G379" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H379">
         <v>19</v>
@@ -13165,13 +13165,13 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F380" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G380" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H380">
         <v>33</v>
@@ -13197,13 +13197,13 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F381" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G381" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H381">
         <v>17</v>
@@ -13229,13 +13229,13 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F382" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G382" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H382">
         <v>27</v>
@@ -13261,13 +13261,13 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F383" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G383" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H383">
         <v>23</v>
@@ -13293,13 +13293,13 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F384" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G384" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H384">
         <v>27</v>
@@ -13325,13 +13325,13 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F385" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G385" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H385">
         <v>24</v>
@@ -13357,13 +13357,13 @@
         <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F386" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G386" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H386">
         <v>27</v>
@@ -13389,13 +13389,13 @@
         <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F387" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G387" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H387">
         <v>20</v>
@@ -13421,13 +13421,13 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F388" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G388" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H388">
         <v>54</v>
@@ -13453,13 +13453,13 @@
         <v>11</v>
       </c>
       <c r="E389" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F389" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G389" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H389">
         <v>19</v>
@@ -13485,13 +13485,13 @@
         <v>11</v>
       </c>
       <c r="E390" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F390" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G390" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H390">
         <v>17</v>
@@ -13517,13 +13517,13 @@
         <v>11</v>
       </c>
       <c r="E391" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F391" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G391" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H391">
         <v>16</v>
@@ -13549,13 +13549,13 @@
         <v>11</v>
       </c>
       <c r="E392" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F392" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G392" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H392">
         <v>17</v>
@@ -13581,13 +13581,13 @@
         <v>11</v>
       </c>
       <c r="E393" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F393" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G393" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H393">
         <v>16</v>
@@ -13616,10 +13616,10 @@
         <v>12</v>
       </c>
       <c r="F394" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G394" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H394">
         <v>20</v>
@@ -13645,13 +13645,13 @@
         <v>11</v>
       </c>
       <c r="E395" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F395" t="s">
         <v>12</v>
       </c>
       <c r="G395" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H395">
         <v>12</v>
@@ -13677,13 +13677,13 @@
         <v>11</v>
       </c>
       <c r="E396" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F396" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G396" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H396">
         <v>23</v>
@@ -13709,13 +13709,13 @@
         <v>11</v>
       </c>
       <c r="E397" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F397" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G397" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H397">
         <v>10</v>
@@ -13741,13 +13741,13 @@
         <v>11</v>
       </c>
       <c r="E398" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F398" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G398" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H398">
         <v>27</v>
@@ -13773,13 +13773,13 @@
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F399" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G399" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H399">
         <v>23</v>
@@ -13805,13 +13805,13 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F400" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G400" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H400">
         <v>34</v>
@@ -13837,13 +13837,13 @@
         <v>11</v>
       </c>
       <c r="E401" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F401" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G401" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H401">
         <v>23</v>
@@ -13869,13 +13869,13 @@
         <v>11</v>
       </c>
       <c r="E402" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F402" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G402" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H402">
         <v>36</v>
@@ -13901,13 +13901,13 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F403" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G403" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H403">
         <v>22</v>
@@ -13933,13 +13933,13 @@
         <v>11</v>
       </c>
       <c r="E404" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F404" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G404" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H404">
         <v>48</v>
@@ -13965,13 +13965,13 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F405" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G405" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H405">
         <v>22</v>
@@ -13997,13 +13997,13 @@
         <v>11</v>
       </c>
       <c r="E406" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F406" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G406" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H406">
         <v>16</v>
@@ -14029,13 +14029,13 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F407" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G407" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H407">
         <v>14</v>
@@ -14061,13 +14061,13 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F408" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G408" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H408">
         <v>34</v>
@@ -14093,13 +14093,13 @@
         <v>11</v>
       </c>
       <c r="E409" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F409" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G409" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H409">
         <v>28</v>
@@ -14125,13 +14125,13 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F410" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G410" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H410">
         <v>30</v>
@@ -14157,13 +14157,13 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F411" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G411" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H411">
         <v>24</v>
@@ -14189,13 +14189,13 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F412" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G412" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H412">
         <v>35</v>
@@ -14221,13 +14221,13 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F413" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G413" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H413">
         <v>7</v>
@@ -14253,13 +14253,13 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F414" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G414" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H414">
         <v>23</v>
@@ -14285,13 +14285,13 @@
         <v>11</v>
       </c>
       <c r="E415" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F415" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G415" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H415">
         <v>17</v>
@@ -14317,13 +14317,13 @@
         <v>11</v>
       </c>
       <c r="E416" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F416" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G416" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H416">
         <v>27</v>
@@ -14349,13 +14349,13 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F417" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G417" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H417">
         <v>13</v>
@@ -14381,13 +14381,13 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F418" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G418" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H418">
         <v>21</v>
@@ -14413,13 +14413,13 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F419" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G419" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H419">
         <v>13</v>
@@ -14445,13 +14445,13 @@
         <v>11</v>
       </c>
       <c r="E420" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F420" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G420" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H420">
         <v>39</v>
@@ -14477,13 +14477,13 @@
         <v>11</v>
       </c>
       <c r="E421" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F421" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G421" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H421">
         <v>36</v>
@@ -14509,13 +14509,13 @@
         <v>11</v>
       </c>
       <c r="E422" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F422" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G422" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H422">
         <v>13</v>
@@ -14541,13 +14541,13 @@
         <v>11</v>
       </c>
       <c r="E423" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F423" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G423" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H423">
         <v>3</v>
@@ -14576,10 +14576,10 @@
         <v>12</v>
       </c>
       <c r="F424" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G424" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H424">
         <v>32</v>
@@ -14605,13 +14605,13 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F425" t="s">
         <v>12</v>
       </c>
       <c r="G425" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H425">
         <v>29</v>
@@ -14637,13 +14637,13 @@
         <v>11</v>
       </c>
       <c r="E426" t="s">
+        <v>15</v>
+      </c>
+      <c r="F426" t="s">
         <v>16</v>
       </c>
-      <c r="F426" t="s">
-        <v>17</v>
-      </c>
       <c r="G426" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H426">
         <v>21</v>
@@ -14669,13 +14669,13 @@
         <v>11</v>
       </c>
       <c r="E427" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F427" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G427" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H427">
         <v>18</v>
@@ -14701,13 +14701,13 @@
         <v>11</v>
       </c>
       <c r="E428" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F428" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G428" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H428">
         <v>24</v>
@@ -14733,13 +14733,13 @@
         <v>11</v>
       </c>
       <c r="E429" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F429" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G429" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H429">
         <v>16</v>
@@ -14765,13 +14765,13 @@
         <v>11</v>
       </c>
       <c r="E430" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F430" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G430" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H430">
         <v>25</v>
@@ -14797,13 +14797,13 @@
         <v>11</v>
       </c>
       <c r="E431" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F431" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G431" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H431">
         <v>20</v>
@@ -14829,13 +14829,13 @@
         <v>11</v>
       </c>
       <c r="E432" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F432" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G432" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H432">
         <v>40</v>
@@ -14861,13 +14861,13 @@
         <v>11</v>
       </c>
       <c r="E433" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F433" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G433" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H433">
         <v>34</v>
@@ -14893,13 +14893,13 @@
         <v>11</v>
       </c>
       <c r="E434" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F434" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G434" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H434">
         <v>20</v>
@@ -14925,13 +14925,13 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F435" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G435" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H435">
         <v>17</v>
@@ -14957,13 +14957,13 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F436" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G436" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H436">
         <v>30</v>
@@ -14989,13 +14989,13 @@
         <v>11</v>
       </c>
       <c r="E437" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F437" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G437" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H437">
         <v>24</v>
@@ -15021,13 +15021,13 @@
         <v>11</v>
       </c>
       <c r="E438" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F438" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G438" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H438">
         <v>24</v>
@@ -15053,13 +15053,13 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F439" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G439" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H439">
         <v>15</v>
@@ -15085,13 +15085,13 @@
         <v>11</v>
       </c>
       <c r="E440" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F440" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G440" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H440">
         <v>30</v>
@@ -15117,13 +15117,13 @@
         <v>11</v>
       </c>
       <c r="E441" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F441" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G441" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H441">
         <v>24</v>
@@ -15149,13 +15149,13 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F442" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G442" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H442">
         <v>34</v>
@@ -15181,13 +15181,13 @@
         <v>11</v>
       </c>
       <c r="E443" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F443" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G443" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H443">
         <v>23</v>
@@ -15213,13 +15213,13 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F444" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G444" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H444">
         <v>17</v>
@@ -15245,13 +15245,13 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F445" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G445" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H445">
         <v>14</v>
@@ -15277,13 +15277,13 @@
         <v>11</v>
       </c>
       <c r="E446" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F446" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G446" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H446">
         <v>20</v>
@@ -15309,13 +15309,13 @@
         <v>11</v>
       </c>
       <c r="E447" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F447" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G447" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H447">
         <v>12</v>
@@ -15341,13 +15341,13 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F448" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G448" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H448">
         <v>24</v>
@@ -15373,13 +15373,13 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F449" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G449" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H449">
         <v>12</v>
@@ -15405,13 +15405,13 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F450" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G450" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H450">
         <v>19</v>
@@ -15437,13 +15437,13 @@
         <v>11</v>
       </c>
       <c r="E451" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F451" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G451" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H451">
         <v>3</v>
@@ -15469,13 +15469,13 @@
         <v>11</v>
       </c>
       <c r="E452" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F452" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G452" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H452">
         <v>17</v>
@@ -15501,13 +15501,13 @@
         <v>11</v>
       </c>
       <c r="E453" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F453" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G453" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H453">
         <v>9</v>
@@ -15536,10 +15536,10 @@
         <v>12</v>
       </c>
       <c r="F454" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G454" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H454">
         <v>35</v>
@@ -15565,13 +15565,13 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F455" t="s">
         <v>12</v>
       </c>
       <c r="G455" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H455">
         <v>13</v>
@@ -15597,13 +15597,13 @@
         <v>11</v>
       </c>
       <c r="E456" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F456" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G456" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H456">
         <v>37</v>
@@ -15629,13 +15629,13 @@
         <v>11</v>
       </c>
       <c r="E457" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F457" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G457" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H457">
         <v>23</v>
@@ -15661,13 +15661,13 @@
         <v>11</v>
       </c>
       <c r="E458" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F458" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G458" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H458">
         <v>22</v>
@@ -15693,13 +15693,13 @@
         <v>11</v>
       </c>
       <c r="E459" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F459" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G459" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H459">
         <v>18</v>
@@ -15725,13 +15725,13 @@
         <v>11</v>
       </c>
       <c r="E460" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F460" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G460" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H460">
         <v>17</v>
@@ -15757,13 +15757,13 @@
         <v>11</v>
       </c>
       <c r="E461" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F461" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G461" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H461">
         <v>10</v>
@@ -15789,13 +15789,13 @@
         <v>11</v>
       </c>
       <c r="E462" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F462" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G462" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H462">
         <v>19</v>
@@ -15821,13 +15821,13 @@
         <v>11</v>
       </c>
       <c r="E463" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F463" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G463" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H463">
         <v>14</v>
@@ -15853,13 +15853,13 @@
         <v>11</v>
       </c>
       <c r="E464" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F464" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G464" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H464">
         <v>24</v>
@@ -15885,13 +15885,13 @@
         <v>11</v>
       </c>
       <c r="E465" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F465" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G465" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H465">
         <v>10</v>
@@ -15917,13 +15917,13 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F466" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G466" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H466">
         <v>27</v>
@@ -15949,13 +15949,13 @@
         <v>11</v>
       </c>
       <c r="E467" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F467" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G467" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H467">
         <v>24</v>
@@ -15981,13 +15981,13 @@
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F468" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G468" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H468">
         <v>37</v>
@@ -16013,13 +16013,13 @@
         <v>11</v>
       </c>
       <c r="E469" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F469" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G469" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H469">
         <v>20</v>
@@ -16045,13 +16045,13 @@
         <v>11</v>
       </c>
       <c r="E470" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F470" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G470" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H470">
         <v>40</v>
@@ -16077,13 +16077,13 @@
         <v>11</v>
       </c>
       <c r="E471" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F471" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G471" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H471">
         <v>34</v>
@@ -16109,13 +16109,13 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F472" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G472" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H472">
         <v>13</v>
@@ -16141,13 +16141,13 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F473" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G473" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H473">
         <v>10</v>
@@ -16173,13 +16173,13 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F474" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G474" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H474">
         <v>26</v>
@@ -16205,13 +16205,13 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F475" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G475" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H475">
         <v>20</v>
@@ -16237,13 +16237,13 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F476" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G476" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H476">
         <v>51</v>
@@ -16269,13 +16269,13 @@
         <v>11</v>
       </c>
       <c r="E477" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F477" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G477" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H477">
         <v>14</v>
@@ -16301,13 +16301,13 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F478" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G478" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H478">
         <v>19</v>
@@ -16333,13 +16333,13 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F479" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G479" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H479">
         <v>16</v>
@@ -16365,13 +16365,13 @@
         <v>11</v>
       </c>
       <c r="E480" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F480" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G480" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H480">
         <v>20</v>
@@ -16397,13 +16397,13 @@
         <v>11</v>
       </c>
       <c r="E481" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F481" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G481" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H481">
         <v>3</v>
@@ -16429,13 +16429,13 @@
         <v>11</v>
       </c>
       <c r="E482" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F482" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G482" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H482">
         <v>27</v>
@@ -16461,13 +16461,13 @@
         <v>11</v>
       </c>
       <c r="E483" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F483" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G483" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H483">
         <v>13</v>
@@ -16493,13 +16493,13 @@
         <v>11</v>
       </c>
       <c r="E484" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F484" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G484" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H484">
         <v>20</v>
@@ -16525,13 +16525,13 @@
         <v>11</v>
       </c>
       <c r="E485" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F485" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G485" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H485">
         <v>19</v>
@@ -16557,13 +16557,13 @@
         <v>11</v>
       </c>
       <c r="E486" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F486" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G486" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H486">
         <v>30</v>
@@ -16589,13 +16589,13 @@
         <v>11</v>
       </c>
       <c r="E487" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F487" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G487" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H487">
         <v>24</v>
@@ -16621,13 +16621,13 @@
         <v>11</v>
       </c>
       <c r="E488" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F488" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G488" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H488">
         <v>41</v>
@@ -16653,13 +16653,13 @@
         <v>11</v>
       </c>
       <c r="E489" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F489" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G489" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H489">
         <v>10</v>
@@ -16685,13 +16685,13 @@
         <v>11</v>
       </c>
       <c r="E490" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F490" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G490" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H490">
         <v>24</v>
@@ -16717,13 +16717,13 @@
         <v>11</v>
       </c>
       <c r="E491" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F491" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G491" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H491">
         <v>10</v>
@@ -16749,13 +16749,13 @@
         <v>11</v>
       </c>
       <c r="E492" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F492" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G492" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H492">
         <v>38</v>
@@ -16781,13 +16781,13 @@
         <v>11</v>
       </c>
       <c r="E493" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F493" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G493" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H493">
         <v>10</v>
@@ -16813,13 +16813,13 @@
         <v>11</v>
       </c>
       <c r="E494" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F494" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G494" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H494">
         <v>27</v>
@@ -16845,13 +16845,13 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F495" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G495" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H495">
         <v>24</v>
@@ -16877,13 +16877,13 @@
         <v>11</v>
       </c>
       <c r="E496" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F496" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G496" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H496">
         <v>31</v>
@@ -16909,13 +16909,13 @@
         <v>11</v>
       </c>
       <c r="E497" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F497" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G497" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H497">
         <v>3</v>
@@ -16941,13 +16941,13 @@
         <v>11</v>
       </c>
       <c r="E498" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F498" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G498" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H498">
         <v>23</v>
@@ -16973,13 +16973,13 @@
         <v>11</v>
       </c>
       <c r="E499" t="s">
+        <v>29</v>
+      </c>
+      <c r="F499" t="s">
         <v>30</v>
       </c>
-      <c r="F499" t="s">
-        <v>31</v>
-      </c>
       <c r="G499" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H499">
         <v>21</v>
@@ -17005,13 +17005,13 @@
         <v>11</v>
       </c>
       <c r="E500" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F500" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G500" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H500">
         <v>20</v>
@@ -17037,13 +17037,13 @@
         <v>11</v>
       </c>
       <c r="E501" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F501" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G501" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H501">
         <v>10</v>
@@ -17069,13 +17069,13 @@
         <v>11</v>
       </c>
       <c r="E502" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F502" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G502" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H502">
         <v>23</v>
@@ -17101,13 +17101,13 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F503" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G503" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H503">
         <v>6</v>
@@ -17133,13 +17133,13 @@
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F504" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G504" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H504">
         <v>37</v>
@@ -17165,13 +17165,13 @@
         <v>11</v>
       </c>
       <c r="E505" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F505" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G505" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H505">
         <v>34</v>
@@ -17197,13 +17197,13 @@
         <v>11</v>
       </c>
       <c r="E506" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F506" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G506" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H506">
         <v>41</v>
@@ -17229,13 +17229,13 @@
         <v>11</v>
       </c>
       <c r="E507" t="s">
+        <v>35</v>
+      </c>
+      <c r="F507" t="s">
         <v>36</v>
       </c>
-      <c r="F507" t="s">
-        <v>37</v>
-      </c>
       <c r="G507" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H507">
         <v>17</v>
@@ -17261,13 +17261,13 @@
         <v>11</v>
       </c>
       <c r="E508" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F508" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G508" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H508">
         <v>31</v>
@@ -17293,13 +17293,13 @@
         <v>11</v>
       </c>
       <c r="E509" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F509" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G509" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H509">
         <v>10</v>
@@ -17325,13 +17325,13 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F510" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G510" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H510">
         <v>16</v>
@@ -17357,13 +17357,13 @@
         <v>11</v>
       </c>
       <c r="E511" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F511" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G511" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H511">
         <v>13</v>
@@ -17389,13 +17389,13 @@
         <v>11</v>
       </c>
       <c r="E512" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F512" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G512" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H512">
         <v>31</v>
@@ -17421,13 +17421,13 @@
         <v>11</v>
       </c>
       <c r="E513" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F513" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G513" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H513">
         <v>13</v>
@@ -17453,13 +17453,13 @@
         <v>11</v>
       </c>
       <c r="E514" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F514" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G514" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H514">
         <v>20</v>
@@ -17485,13 +17485,13 @@
         <v>11</v>
       </c>
       <c r="E515" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F515" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G515" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H515">
         <v>16</v>
@@ -17520,10 +17520,10 @@
         <v>12</v>
       </c>
       <c r="F516" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G516" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H516">
         <v>35</v>
@@ -17549,13 +17549,13 @@
         <v>11</v>
       </c>
       <c r="E517" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F517" t="s">
         <v>12</v>
       </c>
       <c r="G517" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H517">
         <v>23</v>
@@ -17581,13 +17581,13 @@
         <v>11</v>
       </c>
       <c r="E518" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F518" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G518" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H518">
         <v>27</v>
@@ -17613,13 +17613,13 @@
         <v>11</v>
       </c>
       <c r="E519" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F519" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G519" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H519">
         <v>16</v>
@@ -17645,13 +17645,13 @@
         <v>11</v>
       </c>
       <c r="E520" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F520" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G520" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H520">
         <v>30</v>
@@ -17677,13 +17677,13 @@
         <v>11</v>
       </c>
       <c r="E521" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F521" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G521" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H521">
         <v>17</v>
@@ -17709,13 +17709,13 @@
         <v>11</v>
       </c>
       <c r="E522" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F522" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G522" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H522">
         <v>10</v>
@@ -17741,13 +17741,13 @@
         <v>11</v>
       </c>
       <c r="E523" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F523" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G523" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H523">
         <v>7</v>
@@ -17773,13 +17773,13 @@
         <v>11</v>
       </c>
       <c r="E524" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F524" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G524" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H524">
         <v>29</v>
@@ -17805,13 +17805,13 @@
         <v>11</v>
       </c>
       <c r="E525" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F525" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G525" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H525">
         <v>13</v>
@@ -17837,13 +17837,13 @@
         <v>11</v>
       </c>
       <c r="E526" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F526" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G526" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H526">
         <v>28</v>
@@ -17869,13 +17869,13 @@
         <v>11</v>
       </c>
       <c r="E527" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F527" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G527" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H527">
         <v>14</v>
@@ -17901,13 +17901,13 @@
         <v>11</v>
       </c>
       <c r="E528" t="s">
+        <v>23</v>
+      </c>
+      <c r="F528" t="s">
         <v>24</v>
       </c>
-      <c r="F528" t="s">
-        <v>25</v>
-      </c>
       <c r="G528" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H528">
         <v>32</v>
@@ -17933,13 +17933,13 @@
         <v>11</v>
       </c>
       <c r="E529" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F529" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G529" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H529">
         <v>31</v>
@@ -17965,13 +17965,13 @@
         <v>11</v>
       </c>
       <c r="E530" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F530" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G530" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H530">
         <v>11</v>
@@ -17997,13 +17997,13 @@
         <v>11</v>
       </c>
       <c r="E531" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F531" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G531" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H531">
         <v>6</v>
@@ -18029,13 +18029,13 @@
         <v>11</v>
       </c>
       <c r="E532" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F532" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G532" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H532">
         <v>38</v>
@@ -18061,13 +18061,13 @@
         <v>11</v>
       </c>
       <c r="E533" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F533" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G533" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H533">
         <v>13</v>
@@ -18093,13 +18093,13 @@
         <v>11</v>
       </c>
       <c r="E534" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F534" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G534" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H534">
         <v>26</v>
@@ -18125,13 +18125,13 @@
         <v>11</v>
       </c>
       <c r="E535" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F535" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G535" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H535">
         <v>6</v>
@@ -18157,13 +18157,13 @@
         <v>11</v>
       </c>
       <c r="E536" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F536" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G536" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H536">
         <v>31</v>
@@ -18189,13 +18189,13 @@
         <v>11</v>
       </c>
       <c r="E537" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F537" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G537" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H537">
         <v>28</v>
@@ -18221,13 +18221,13 @@
         <v>11</v>
       </c>
       <c r="E538" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F538" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G538" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H538">
         <v>22</v>
@@ -18253,13 +18253,13 @@
         <v>11</v>
       </c>
       <c r="E539" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F539" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G539" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H539">
         <v>16</v>
@@ -18285,13 +18285,13 @@
         <v>11</v>
       </c>
       <c r="E540" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F540" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="G540" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H540">
         <v>19</v>
@@ -18317,13 +18317,13 @@
         <v>11</v>
       </c>
       <c r="E541" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="F541" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G541" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H541">
         <v>16</v>
@@ -18349,13 +18349,13 @@
         <v>11</v>
       </c>
       <c r="E542" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F542" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G542" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H542">
         <v>20</v>
@@ -18381,13 +18381,13 @@
         <v>11</v>
       </c>
       <c r="E543" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F543" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G543" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H543">
         <v>16</v>
@@ -18407,19 +18407,19 @@
         <v>2022</v>
       </c>
       <c r="C544" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D544" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E544" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F544" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G544" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H544">
         <v>41</v>
@@ -18439,19 +18439,19 @@
         <v>2022</v>
       </c>
       <c r="C545" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D545" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E545" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F545" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G545" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H545">
         <v>23</v>
@@ -18471,19 +18471,19 @@
         <v>2022</v>
       </c>
       <c r="C546" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D546" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E546" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F546" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G546" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H546">
         <v>31</v>
@@ -18503,19 +18503,19 @@
         <v>2022</v>
       </c>
       <c r="C547" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D547" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E547" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F547" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G547" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H547">
         <v>30</v>
@@ -18535,19 +18535,19 @@
         <v>2022</v>
       </c>
       <c r="C548" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D548" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E548" t="s">
         <v>12</v>
       </c>
       <c r="F548" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G548" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H548">
         <v>34</v>
@@ -18567,19 +18567,19 @@
         <v>2022</v>
       </c>
       <c r="C549" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D549" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E549" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F549" t="s">
         <v>12</v>
       </c>
       <c r="G549" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H549">
         <v>31</v>
@@ -18599,19 +18599,19 @@
         <v>2022</v>
       </c>
       <c r="C550" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D550" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E550" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F550" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G550" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H550">
         <v>31</v>
@@ -18631,19 +18631,19 @@
         <v>2022</v>
       </c>
       <c r="C551" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D551" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E551" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F551" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G551" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H551">
         <v>24</v>
@@ -18663,19 +18663,19 @@
         <v>2022</v>
       </c>
       <c r="C552" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D552" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E552" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F552" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G552" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H552">
         <v>24</v>
@@ -18695,19 +18695,19 @@
         <v>2022</v>
       </c>
       <c r="C553" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D553" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E553" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F553" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G553" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H553">
         <v>17</v>
@@ -18727,19 +18727,19 @@
         <v>2022</v>
       </c>
       <c r="C554" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D554" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E554" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F554" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G554" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H554">
         <v>31</v>
@@ -18759,19 +18759,19 @@
         <v>2022</v>
       </c>
       <c r="C555" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D555" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E555" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F555" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G555" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H555">
         <v>14</v>
@@ -18791,19 +18791,19 @@
         <v>2022</v>
       </c>
       <c r="C556" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D556" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E556" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F556" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G556" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H556">
         <v>27</v>
@@ -18823,19 +18823,19 @@
         <v>2022</v>
       </c>
       <c r="C557" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D557" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E557" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F557" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G557" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H557">
         <v>20</v>
@@ -18855,19 +18855,19 @@
         <v>2022</v>
       </c>
       <c r="C558" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D558" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E558" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F558" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G558" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H558">
         <v>38</v>
@@ -18887,19 +18887,19 @@
         <v>2022</v>
       </c>
       <c r="C559" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D559" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E559" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F559" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G559" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H559">
         <v>7</v>
@@ -18919,19 +18919,19 @@
         <v>2022</v>
       </c>
       <c r="C560" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D560" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E560" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F560" t="s">
         <v>12</v>
       </c>
       <c r="G560" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H560">
         <v>27</v>
@@ -18951,19 +18951,19 @@
         <v>2022</v>
       </c>
       <c r="C561" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D561" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E561" t="s">
         <v>12</v>
       </c>
       <c r="F561" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G561" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H561">
         <v>10</v>
@@ -18983,19 +18983,19 @@
         <v>2022</v>
       </c>
       <c r="C562" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D562" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E562" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F562" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G562" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H562">
         <v>19</v>
@@ -19015,19 +19015,19 @@
         <v>2022</v>
       </c>
       <c r="C563" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D563" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E563" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F563" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G563" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H563">
         <v>12</v>
@@ -19047,19 +19047,19 @@
         <v>2022</v>
       </c>
       <c r="C564" t="s">
+        <v>43</v>
+      </c>
+      <c r="D564" t="s">
         <v>46</v>
       </c>
-      <c r="D564" t="s">
-        <v>49</v>
-      </c>
       <c r="E564" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F564" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G564" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H564">
         <v>31</v>
@@ -19079,19 +19079,19 @@
         <v>2022</v>
       </c>
       <c r="C565" t="s">
+        <v>43</v>
+      </c>
+      <c r="D565" t="s">
         <v>46</v>
       </c>
-      <c r="D565" t="s">
-        <v>49</v>
-      </c>
       <c r="E565" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F565" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G565" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H565">
         <v>7</v>
@@ -19111,19 +19111,19 @@
         <v>2022</v>
       </c>
       <c r="C566" t="s">
+        <v>43</v>
+      </c>
+      <c r="D566" t="s">
         <v>46</v>
       </c>
-      <c r="D566" t="s">
-        <v>49</v>
-      </c>
       <c r="E566" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F566" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G566" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H566">
         <v>23</v>
@@ -19143,19 +19143,19 @@
         <v>2022</v>
       </c>
       <c r="C567" t="s">
+        <v>43</v>
+      </c>
+      <c r="D567" t="s">
         <v>46</v>
       </c>
-      <c r="D567" t="s">
-        <v>49</v>
-      </c>
       <c r="E567" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F567" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G567" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H567">
         <v>20</v>
@@ -19175,19 +19175,19 @@
         <v>2022</v>
       </c>
       <c r="C568" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D568" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E568" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F568" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G568" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H568">
         <v>38</v>
@@ -19207,19 +19207,19 @@
         <v>2022</v>
       </c>
       <c r="C569" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D569" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E569" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F569" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G569" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H569">
         <v>35</v>
